--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121282919</v>
+        <v>121283094</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691552</v>
+        <v>691621</v>
       </c>
       <c r="R2" t="n">
-        <v>7138138</v>
+        <v>7138187</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121282921</v>
       </c>
       <c r="B3" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R4" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283094</v>
+        <v>121282921</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>90674</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691621</v>
+        <v>691522</v>
       </c>
       <c r="R2" t="n">
-        <v>7138187</v>
+        <v>7138133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121282921</v>
+        <v>121282919</v>
       </c>
       <c r="B3" t="n">
-        <v>90662</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691522</v>
+        <v>691552</v>
       </c>
       <c r="R3" t="n">
-        <v>7138133</v>
+        <v>7138138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121282919</v>
+        <v>121283094</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691552</v>
+        <v>691621</v>
       </c>
       <c r="R4" t="n">
-        <v>7138138</v>
+        <v>7138187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121282921</v>
+        <v>121282919</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
+        <v>91986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691522</v>
+        <v>691552</v>
       </c>
       <c r="R2" t="n">
-        <v>7138133</v>
+        <v>7138138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121282919</v>
+        <v>121282921</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>90675</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691552</v>
+        <v>691522</v>
       </c>
       <c r="R3" t="n">
-        <v>7138138</v>
+        <v>7138133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>121283094</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121282919</v>
+        <v>121283094</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691552</v>
+        <v>691621</v>
       </c>
       <c r="R2" t="n">
-        <v>7138138</v>
+        <v>7138187</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121282921</v>
       </c>
       <c r="B3" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R4" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B2" t="n">
         <v>91989</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R2" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121282921</v>
+        <v>121283094</v>
       </c>
       <c r="B3" t="n">
-        <v>90678</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691522</v>
+        <v>691621</v>
       </c>
       <c r="R3" t="n">
-        <v>7138133</v>
+        <v>7138187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121282919</v>
+        <v>121282921</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>90678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691552</v>
+        <v>691522</v>
       </c>
       <c r="R4" t="n">
-        <v>7138138</v>
+        <v>7138133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121282919</v>
+        <v>121282921</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
+        <v>90684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691552</v>
+        <v>691522</v>
       </c>
       <c r="R2" t="n">
-        <v>7138138</v>
+        <v>7138133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R3" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121282921</v>
+        <v>121283094</v>
       </c>
       <c r="B4" t="n">
-        <v>90678</v>
+        <v>91995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691522</v>
+        <v>691621</v>
       </c>
       <c r="R4" t="n">
-        <v>7138133</v>
+        <v>7138187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,6 +986,3050 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121585729</v>
+      </c>
+      <c r="B5" t="n">
+        <v>77993</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>691479</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7138224</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121585692</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91996</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>691607</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7138153</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121585743</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89419</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>691607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7138152</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121585750</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>691554</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7138209</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121585731</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89769</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>691597</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7138152</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121585657</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90685</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>691707</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7138221</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121585633</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691813</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7138277</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121585699</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92012</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691577</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7138141</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121585695</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78254</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>691496</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7138229</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121585704</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91988</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>691560</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7138133</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121585758</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>691640</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7138220</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121585610</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>691709</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7138152</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121585712</v>
+      </c>
+      <c r="B17" t="n">
+        <v>77993</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>691552</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7138135</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121585613</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>691729</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7138280</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121585719</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>691548</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7138206</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121585716</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>691596</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7138152</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121585752</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57509</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>691505</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7138216</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121585753</v>
+      </c>
+      <c r="B22" t="n">
+        <v>77993</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>691507</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7138234</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121585642</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90667</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>112</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>691703</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7138195</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121585582</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>691728</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7138256</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121585616</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90685</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>691708</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7138202</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121585772</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79227</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>691496</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7138158</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121585694</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78643</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>185</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>691483</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7138215</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121585723</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>691505</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7138208</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121585609</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90667</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>112</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vittanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>691707</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7138212</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121585714</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91996</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>691522</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7138144</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121282921</v>
+        <v>121283094</v>
       </c>
       <c r="B2" t="n">
-        <v>90684</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691522</v>
+        <v>691621</v>
       </c>
       <c r="R2" t="n">
-        <v>7138133</v>
+        <v>7138187</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121282919</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283094</v>
+        <v>121282921</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>90685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691621</v>
+        <v>691522</v>
       </c>
       <c r="R4" t="n">
-        <v>7138187</v>
+        <v>7138133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585729</v>
+        <v>121585704</v>
       </c>
       <c r="B5" t="n">
-        <v>77993</v>
+        <v>91988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691479</v>
+        <v>691560</v>
       </c>
       <c r="R5" t="n">
-        <v>7138224</v>
+        <v>7138133</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585692</v>
+        <v>121585723</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691607</v>
+        <v>691505</v>
       </c>
       <c r="R6" t="n">
-        <v>7138153</v>
+        <v>7138208</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585750</v>
+        <v>121585772</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>79227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,43 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691554</v>
+        <v>691496</v>
       </c>
       <c r="R8" t="n">
-        <v>7138209</v>
+        <v>7138158</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1582,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585657</v>
+        <v>121585642</v>
       </c>
       <c r="B10" t="n">
-        <v>90685</v>
+        <v>90667</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,25 +1585,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691707</v>
+        <v>691703</v>
       </c>
       <c r="R10" t="n">
-        <v>7138221</v>
+        <v>7138195</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585633</v>
+        <v>121585695</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>78254</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,37 +1705,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691813</v>
+        <v>691496</v>
       </c>
       <c r="R11" t="n">
-        <v>7138277</v>
+        <v>7138229</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1773,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585699</v>
+        <v>121585714</v>
       </c>
       <c r="B12" t="n">
-        <v>92012</v>
+        <v>91996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,25 +1817,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691577</v>
+        <v>691522</v>
       </c>
       <c r="R12" t="n">
-        <v>7138141</v>
+        <v>7138144</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1930,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585695</v>
+        <v>121585657</v>
       </c>
       <c r="B13" t="n">
-        <v>78254</v>
+        <v>90685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,41 +1933,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691496</v>
+        <v>691707</v>
       </c>
       <c r="R13" t="n">
-        <v>7138229</v>
+        <v>7138221</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585704</v>
+        <v>121585613</v>
       </c>
       <c r="B14" t="n">
-        <v>91988</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,37 +2053,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691560</v>
+        <v>691729</v>
       </c>
       <c r="R14" t="n">
-        <v>7138133</v>
+        <v>7138280</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2121,7 +2112,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2122,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585758</v>
+        <v>121585633</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,46 +2169,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691640</v>
+        <v>691813</v>
       </c>
       <c r="R15" t="n">
-        <v>7138220</v>
+        <v>7138277</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2246,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585610</v>
+        <v>121585609</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>90667</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2285,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691709</v>
+        <v>691707</v>
       </c>
       <c r="R16" t="n">
-        <v>7138152</v>
+        <v>7138212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585712</v>
+        <v>121585716</v>
       </c>
       <c r="B17" t="n">
-        <v>77993</v>
+        <v>92000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,25 +2397,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691552</v>
+        <v>691596</v>
       </c>
       <c r="R17" t="n">
-        <v>7138135</v>
+        <v>7138152</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2519,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585613</v>
+        <v>121585610</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2559,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691729</v>
+        <v>691709</v>
       </c>
       <c r="R18" t="n">
-        <v>7138280</v>
+        <v>7138152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2635,7 +2617,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585719</v>
+        <v>121585582</v>
       </c>
       <c r="B19" t="n">
         <v>90720</v>
@@ -2671,17 +2653,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691548</v>
+        <v>691728</v>
       </c>
       <c r="R19" t="n">
-        <v>7138206</v>
+        <v>7138256</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2751,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121585716</v>
+        <v>121585699</v>
       </c>
       <c r="B20" t="n">
-        <v>92000</v>
+        <v>92012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,25 +2745,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2791,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691596</v>
+        <v>691577</v>
       </c>
       <c r="R20" t="n">
-        <v>7138152</v>
+        <v>7138141</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2867,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585752</v>
+        <v>121585753</v>
       </c>
       <c r="B21" t="n">
-        <v>57509</v>
+        <v>77993</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2883,43 +2865,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691505</v>
+        <v>691507</v>
       </c>
       <c r="R21" t="n">
-        <v>7138216</v>
+        <v>7138234</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2992,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585753</v>
+        <v>121585694</v>
       </c>
       <c r="B22" t="n">
-        <v>77993</v>
+        <v>78643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3008,21 +2981,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3032,10 +3005,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691507</v>
+        <v>691483</v>
       </c>
       <c r="R22" t="n">
-        <v>7138234</v>
+        <v>7138215</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3086,6 +3059,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3108,10 +3082,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585642</v>
+        <v>121585758</v>
       </c>
       <c r="B23" t="n">
-        <v>90667</v>
+        <v>57372</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3124,37 +3098,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691703</v>
+        <v>691640</v>
       </c>
       <c r="R23" t="n">
-        <v>7138195</v>
+        <v>7138220</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3183,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3224,10 +3207,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121585582</v>
+        <v>121585750</v>
       </c>
       <c r="B24" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3240,37 +3223,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691728</v>
+        <v>691554</v>
       </c>
       <c r="R24" t="n">
-        <v>7138256</v>
+        <v>7138209</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3299,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3309,7 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585616</v>
+        <v>121585729</v>
       </c>
       <c r="B25" t="n">
-        <v>90685</v>
+        <v>77993</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3352,41 +3344,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691708</v>
+        <v>691479</v>
       </c>
       <c r="R25" t="n">
-        <v>7138202</v>
+        <v>7138224</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3415,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3425,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3456,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585772</v>
+        <v>121585719</v>
       </c>
       <c r="B26" t="n">
-        <v>79227</v>
+        <v>90720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,21 +3464,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3496,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691496</v>
+        <v>691548</v>
       </c>
       <c r="R26" t="n">
-        <v>7138158</v>
+        <v>7138206</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3572,10 +3564,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121585694</v>
+        <v>121585752</v>
       </c>
       <c r="B27" t="n">
-        <v>78643</v>
+        <v>57509</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3588,34 +3580,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691483</v>
+        <v>691505</v>
       </c>
       <c r="R27" t="n">
-        <v>7138215</v>
+        <v>7138216</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3666,7 +3667,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585723</v>
+        <v>121585616</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,41 +3701,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691505</v>
+        <v>691708</v>
       </c>
       <c r="R28" t="n">
-        <v>7138208</v>
+        <v>7138202</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3805,10 +3805,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585609</v>
+        <v>121585712</v>
       </c>
       <c r="B29" t="n">
-        <v>90667</v>
+        <v>77993</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,37 +3821,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691707</v>
+        <v>691552</v>
       </c>
       <c r="R29" t="n">
-        <v>7138212</v>
+        <v>7138135</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,7 +3921,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585714</v>
+        <v>121585692</v>
       </c>
       <c r="B30" t="n">
         <v>91996</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691522</v>
+        <v>691607</v>
       </c>
       <c r="R30" t="n">
-        <v>7138144</v>
+        <v>7138153</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B2" t="n">
         <v>91996</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R2" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121282919</v>
+        <v>121282921</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>90685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691552</v>
+        <v>691522</v>
       </c>
       <c r="R3" t="n">
-        <v>7138138</v>
+        <v>7138133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121282921</v>
+        <v>121283094</v>
       </c>
       <c r="B4" t="n">
-        <v>90685</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691522</v>
+        <v>691621</v>
       </c>
       <c r="R4" t="n">
-        <v>7138133</v>
+        <v>7138187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585704</v>
+        <v>121585772</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>79227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691560</v>
+        <v>691496</v>
       </c>
       <c r="R5" t="n">
-        <v>7138133</v>
+        <v>7138158</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585723</v>
+        <v>121585731</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>89769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691505</v>
+        <v>691597</v>
       </c>
       <c r="R6" t="n">
-        <v>7138208</v>
+        <v>7138152</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585743</v>
+        <v>121585609</v>
       </c>
       <c r="B7" t="n">
-        <v>89419</v>
+        <v>90667</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,41 +1237,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6286</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691607</v>
+        <v>691707</v>
       </c>
       <c r="R7" t="n">
-        <v>7138152</v>
+        <v>7138212</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585772</v>
+        <v>121585716</v>
       </c>
       <c r="B8" t="n">
-        <v>79227</v>
+        <v>92000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691496</v>
+        <v>691596</v>
       </c>
       <c r="R8" t="n">
-        <v>7138158</v>
+        <v>7138152</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585731</v>
+        <v>121585750</v>
       </c>
       <c r="B9" t="n">
-        <v>89769</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1473,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691597</v>
+        <v>691554</v>
       </c>
       <c r="R9" t="n">
-        <v>7138152</v>
+        <v>7138209</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585642</v>
+        <v>121585610</v>
       </c>
       <c r="B10" t="n">
-        <v>90667</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,21 +1598,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691703</v>
+        <v>691709</v>
       </c>
       <c r="R10" t="n">
-        <v>7138195</v>
+        <v>7138152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585714</v>
+        <v>121585613</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,41 +1826,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691522</v>
+        <v>691729</v>
       </c>
       <c r="R12" t="n">
-        <v>7138144</v>
+        <v>7138280</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585657</v>
+        <v>121585699</v>
       </c>
       <c r="B13" t="n">
-        <v>90685</v>
+        <v>92012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,41 +1942,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691707</v>
+        <v>691577</v>
       </c>
       <c r="R13" t="n">
-        <v>7138221</v>
+        <v>7138141</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585613</v>
+        <v>121585723</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,37 +2062,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691729</v>
+        <v>691505</v>
       </c>
       <c r="R14" t="n">
-        <v>7138280</v>
+        <v>7138208</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2122,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585633</v>
+        <v>121585753</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>77993</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,37 +2178,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691813</v>
+        <v>691507</v>
       </c>
       <c r="R15" t="n">
-        <v>7138277</v>
+        <v>7138234</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585609</v>
+        <v>121585712</v>
       </c>
       <c r="B16" t="n">
-        <v>90667</v>
+        <v>77993</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,37 +2294,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691707</v>
+        <v>691552</v>
       </c>
       <c r="R16" t="n">
-        <v>7138212</v>
+        <v>7138135</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585716</v>
+        <v>121585582</v>
       </c>
       <c r="B17" t="n">
-        <v>92000</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,41 +2406,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691596</v>
+        <v>691728</v>
       </c>
       <c r="R17" t="n">
-        <v>7138152</v>
+        <v>7138256</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585610</v>
+        <v>121585616</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,25 +2522,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2541,10 +2550,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691709</v>
+        <v>691708</v>
       </c>
       <c r="R18" t="n">
-        <v>7138152</v>
+        <v>7138202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2617,7 +2626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585582</v>
+        <v>121585633</v>
       </c>
       <c r="B19" t="n">
         <v>90720</v>
@@ -2657,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691728</v>
+        <v>691813</v>
       </c>
       <c r="R19" t="n">
-        <v>7138256</v>
+        <v>7138277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2733,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121585699</v>
+        <v>121585743</v>
       </c>
       <c r="B20" t="n">
-        <v>92012</v>
+        <v>89419</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,25 +2754,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691577</v>
+        <v>691607</v>
       </c>
       <c r="R20" t="n">
-        <v>7138141</v>
+        <v>7138152</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2849,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585753</v>
+        <v>121585719</v>
       </c>
       <c r="B21" t="n">
-        <v>77993</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,21 +2874,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2889,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691507</v>
+        <v>691548</v>
       </c>
       <c r="R21" t="n">
-        <v>7138234</v>
+        <v>7138206</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2965,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585694</v>
+        <v>121585704</v>
       </c>
       <c r="B22" t="n">
-        <v>78643</v>
+        <v>91988</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2981,21 +2990,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3005,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691483</v>
+        <v>691560</v>
       </c>
       <c r="R22" t="n">
-        <v>7138215</v>
+        <v>7138133</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3059,7 +3068,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3082,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585758</v>
+        <v>121585729</v>
       </c>
       <c r="B23" t="n">
-        <v>57372</v>
+        <v>77993</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,43 +3106,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691640</v>
+        <v>691479</v>
       </c>
       <c r="R23" t="n">
-        <v>7138220</v>
+        <v>7138224</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3166,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3207,10 +3206,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121585750</v>
+        <v>121585694</v>
       </c>
       <c r="B24" t="n">
-        <v>57372</v>
+        <v>78643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3223,43 +3222,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691554</v>
+        <v>691483</v>
       </c>
       <c r="R24" t="n">
-        <v>7138209</v>
+        <v>7138215</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3291,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3291,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,6 +3300,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3332,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585729</v>
+        <v>121585642</v>
       </c>
       <c r="B25" t="n">
-        <v>77993</v>
+        <v>90667</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3348,37 +3339,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691479</v>
+        <v>691703</v>
       </c>
       <c r="R25" t="n">
-        <v>7138224</v>
+        <v>7138195</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3407,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,10 +3439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585719</v>
+        <v>121585714</v>
       </c>
       <c r="B26" t="n">
-        <v>90720</v>
+        <v>91996</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3451,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3479,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691548</v>
+        <v>691522</v>
       </c>
       <c r="R26" t="n">
-        <v>7138206</v>
+        <v>7138144</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3564,10 +3555,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121585752</v>
+        <v>121585758</v>
       </c>
       <c r="B27" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,31 +3571,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3613,10 +3604,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691505</v>
+        <v>691640</v>
       </c>
       <c r="R27" t="n">
-        <v>7138216</v>
+        <v>7138220</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3648,7 +3639,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3649,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3689,10 +3680,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585616</v>
+        <v>121585692</v>
       </c>
       <c r="B28" t="n">
-        <v>90685</v>
+        <v>91996</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3705,37 +3696,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691708</v>
+        <v>691607</v>
       </c>
       <c r="R28" t="n">
-        <v>7138202</v>
+        <v>7138153</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3764,7 +3755,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,7 +3765,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3805,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585712</v>
+        <v>121585657</v>
       </c>
       <c r="B29" t="n">
-        <v>77993</v>
+        <v>90685</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3817,41 +3808,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691552</v>
+        <v>691707</v>
       </c>
       <c r="R29" t="n">
-        <v>7138135</v>
+        <v>7138221</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3880,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3890,7 +3881,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585692</v>
+        <v>121585752</v>
       </c>
       <c r="B30" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3933,38 +3924,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691607</v>
+        <v>691505</v>
       </c>
       <c r="R30" t="n">
-        <v>7138153</v>
+        <v>7138216</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121282919</v>
+        <v>121282921</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>90685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691552</v>
+        <v>691522</v>
       </c>
       <c r="R2" t="n">
-        <v>7138138</v>
+        <v>7138133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121282921</v>
+        <v>121283094</v>
       </c>
       <c r="B3" t="n">
-        <v>90685</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691522</v>
+        <v>691621</v>
       </c>
       <c r="R3" t="n">
-        <v>7138133</v>
+        <v>7138187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B4" t="n">
         <v>91996</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R4" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585772</v>
+        <v>121585609</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>90667</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,37 +1009,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691496</v>
+        <v>691707</v>
       </c>
       <c r="R5" t="n">
-        <v>7138158</v>
+        <v>7138212</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585731</v>
+        <v>121585714</v>
       </c>
       <c r="B6" t="n">
-        <v>89769</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691597</v>
+        <v>691522</v>
       </c>
       <c r="R6" t="n">
-        <v>7138152</v>
+        <v>7138144</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585609</v>
+        <v>121585719</v>
       </c>
       <c r="B7" t="n">
-        <v>90667</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,37 +1241,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691707</v>
+        <v>691548</v>
       </c>
       <c r="R7" t="n">
-        <v>7138212</v>
+        <v>7138206</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585716</v>
+        <v>121585772</v>
       </c>
       <c r="B8" t="n">
-        <v>92000</v>
+        <v>79227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691596</v>
+        <v>691496</v>
       </c>
       <c r="R8" t="n">
-        <v>7138152</v>
+        <v>7138158</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585610</v>
+        <v>121585613</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691709</v>
+        <v>691729</v>
       </c>
       <c r="R10" t="n">
-        <v>7138152</v>
+        <v>7138280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585695</v>
+        <v>121585731</v>
       </c>
       <c r="B11" t="n">
-        <v>78254</v>
+        <v>89769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691496</v>
+        <v>691597</v>
       </c>
       <c r="R11" t="n">
-        <v>7138229</v>
+        <v>7138152</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585613</v>
+        <v>121585616</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,25 +1826,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691729</v>
+        <v>691708</v>
       </c>
       <c r="R12" t="n">
-        <v>7138280</v>
+        <v>7138202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585699</v>
+        <v>121585695</v>
       </c>
       <c r="B13" t="n">
-        <v>92012</v>
+        <v>78254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691577</v>
+        <v>691496</v>
       </c>
       <c r="R13" t="n">
-        <v>7138141</v>
+        <v>7138229</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585753</v>
+        <v>121585743</v>
       </c>
       <c r="B15" t="n">
-        <v>77993</v>
+        <v>89419</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,25 +2174,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691507</v>
+        <v>691607</v>
       </c>
       <c r="R15" t="n">
-        <v>7138234</v>
+        <v>7138152</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585712</v>
+        <v>121585657</v>
       </c>
       <c r="B16" t="n">
-        <v>77993</v>
+        <v>90685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,41 +2290,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691552</v>
+        <v>691707</v>
       </c>
       <c r="R16" t="n">
-        <v>7138135</v>
+        <v>7138221</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585582</v>
+        <v>121585712</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>77993</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,37 +2410,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691728</v>
+        <v>691552</v>
       </c>
       <c r="R17" t="n">
-        <v>7138256</v>
+        <v>7138135</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585616</v>
+        <v>121585729</v>
       </c>
       <c r="B18" t="n">
-        <v>90685</v>
+        <v>77993</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,41 +2522,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691708</v>
+        <v>691479</v>
       </c>
       <c r="R18" t="n">
-        <v>7138202</v>
+        <v>7138224</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585633</v>
+        <v>121585610</v>
       </c>
       <c r="B19" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,21 +2642,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691813</v>
+        <v>691709</v>
       </c>
       <c r="R19" t="n">
-        <v>7138277</v>
+        <v>7138152</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121585743</v>
+        <v>121585753</v>
       </c>
       <c r="B20" t="n">
-        <v>89419</v>
+        <v>77993</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,25 +2754,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6286</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691607</v>
+        <v>691507</v>
       </c>
       <c r="R20" t="n">
-        <v>7138152</v>
+        <v>7138234</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585719</v>
+        <v>121585582</v>
       </c>
       <c r="B21" t="n">
         <v>90720</v>
@@ -2894,17 +2894,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691548</v>
+        <v>691728</v>
       </c>
       <c r="R21" t="n">
-        <v>7138206</v>
+        <v>7138256</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585704</v>
+        <v>121585758</v>
       </c>
       <c r="B22" t="n">
-        <v>91988</v>
+        <v>57372</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,34 +2990,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691560</v>
+        <v>691640</v>
       </c>
       <c r="R22" t="n">
-        <v>7138133</v>
+        <v>7138220</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3049,7 +3058,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3068,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3099,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585729</v>
+        <v>121585704</v>
       </c>
       <c r="B23" t="n">
-        <v>77993</v>
+        <v>91988</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3115,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691479</v>
+        <v>691560</v>
       </c>
       <c r="R23" t="n">
-        <v>7138224</v>
+        <v>7138133</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3206,10 +3215,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121585694</v>
+        <v>121585716</v>
       </c>
       <c r="B24" t="n">
-        <v>78643</v>
+        <v>92000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3218,25 +3227,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3246,10 +3255,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691483</v>
+        <v>691596</v>
       </c>
       <c r="R24" t="n">
-        <v>7138215</v>
+        <v>7138152</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3300,7 +3309,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3323,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585642</v>
+        <v>121585699</v>
       </c>
       <c r="B25" t="n">
-        <v>90667</v>
+        <v>92012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,37 +3347,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691703</v>
+        <v>691577</v>
       </c>
       <c r="R25" t="n">
-        <v>7138195</v>
+        <v>7138141</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3406,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3416,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585714</v>
+        <v>121585752</v>
       </c>
       <c r="B26" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,38 +3459,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691522</v>
+        <v>691505</v>
       </c>
       <c r="R26" t="n">
-        <v>7138144</v>
+        <v>7138216</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3555,10 +3572,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121585758</v>
+        <v>121585692</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3567,47 +3584,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691640</v>
+        <v>691607</v>
       </c>
       <c r="R27" t="n">
-        <v>7138220</v>
+        <v>7138153</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3639,7 +3647,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3657,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3680,10 +3688,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585692</v>
+        <v>121585694</v>
       </c>
       <c r="B28" t="n">
-        <v>91996</v>
+        <v>78643</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,25 +3700,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3720,10 +3728,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691607</v>
+        <v>691483</v>
       </c>
       <c r="R28" t="n">
-        <v>7138153</v>
+        <v>7138215</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3774,6 +3782,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3796,10 +3805,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585657</v>
+        <v>121585633</v>
       </c>
       <c r="B29" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3808,25 +3817,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3836,10 +3845,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691707</v>
+        <v>691813</v>
       </c>
       <c r="R29" t="n">
-        <v>7138221</v>
+        <v>7138277</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3912,10 +3921,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585752</v>
+        <v>121585642</v>
       </c>
       <c r="B30" t="n">
-        <v>57509</v>
+        <v>90667</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3928,46 +3937,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691505</v>
+        <v>691703</v>
       </c>
       <c r="R30" t="n">
-        <v>7138216</v>
+        <v>7138195</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B3" t="n">
         <v>91996</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R3" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121282919</v>
+        <v>121283094</v>
       </c>
       <c r="B4" t="n">
         <v>91996</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691552</v>
+        <v>691621</v>
       </c>
       <c r="R4" t="n">
-        <v>7138138</v>
+        <v>7138187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585609</v>
+        <v>121585772</v>
       </c>
       <c r="B5" t="n">
-        <v>90667</v>
+        <v>79227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,37 +1009,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691707</v>
+        <v>691496</v>
       </c>
       <c r="R5" t="n">
-        <v>7138212</v>
+        <v>7138158</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585714</v>
+        <v>121585743</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>89419</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691522</v>
+        <v>691607</v>
       </c>
       <c r="R6" t="n">
-        <v>7138144</v>
+        <v>7138152</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585719</v>
+        <v>121585753</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>77993</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691548</v>
+        <v>691507</v>
       </c>
       <c r="R7" t="n">
-        <v>7138206</v>
+        <v>7138234</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585772</v>
+        <v>121585633</v>
       </c>
       <c r="B8" t="n">
-        <v>79227</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,37 +1357,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691496</v>
+        <v>691813</v>
       </c>
       <c r="R8" t="n">
-        <v>7138158</v>
+        <v>7138277</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585750</v>
+        <v>121585719</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,43 +1473,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691554</v>
+        <v>691548</v>
       </c>
       <c r="R9" t="n">
-        <v>7138209</v>
+        <v>7138206</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585613</v>
+        <v>121585714</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,41 +1585,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691729</v>
+        <v>691522</v>
       </c>
       <c r="R10" t="n">
-        <v>7138280</v>
+        <v>7138144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,7 +1648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1658,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585731</v>
+        <v>121585695</v>
       </c>
       <c r="B11" t="n">
-        <v>89769</v>
+        <v>78254</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691597</v>
+        <v>691496</v>
       </c>
       <c r="R11" t="n">
-        <v>7138152</v>
+        <v>7138229</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1814,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585616</v>
+        <v>121585613</v>
       </c>
       <c r="B12" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,25 +1817,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691708</v>
+        <v>691729</v>
       </c>
       <c r="R12" t="n">
-        <v>7138202</v>
+        <v>7138280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585695</v>
+        <v>121585699</v>
       </c>
       <c r="B13" t="n">
-        <v>78254</v>
+        <v>92012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,21 +1937,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691496</v>
+        <v>691577</v>
       </c>
       <c r="R13" t="n">
-        <v>7138229</v>
+        <v>7138141</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2046,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585723</v>
+        <v>121585694</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,21 +2053,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691505</v>
+        <v>691483</v>
       </c>
       <c r="R14" t="n">
-        <v>7138208</v>
+        <v>7138215</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2140,6 +2131,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2162,10 +2154,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585743</v>
+        <v>121585752</v>
       </c>
       <c r="B15" t="n">
-        <v>89419</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,38 +2166,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6286</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691607</v>
+        <v>691505</v>
       </c>
       <c r="R15" t="n">
-        <v>7138152</v>
+        <v>7138216</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2278,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585657</v>
+        <v>121585610</v>
       </c>
       <c r="B16" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,25 +2291,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691707</v>
+        <v>691709</v>
       </c>
       <c r="R16" t="n">
-        <v>7138221</v>
+        <v>7138152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2394,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585712</v>
+        <v>121585750</v>
       </c>
       <c r="B17" t="n">
-        <v>77993</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,34 +2411,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691552</v>
+        <v>691554</v>
       </c>
       <c r="R17" t="n">
-        <v>7138135</v>
+        <v>7138209</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585729</v>
+        <v>121585704</v>
       </c>
       <c r="B18" t="n">
-        <v>77993</v>
+        <v>91988</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,21 +2536,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2550,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691479</v>
+        <v>691560</v>
       </c>
       <c r="R18" t="n">
-        <v>7138224</v>
+        <v>7138133</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2626,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585610</v>
+        <v>121585609</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>90667</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,21 +2652,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691709</v>
+        <v>691707</v>
       </c>
       <c r="R19" t="n">
-        <v>7138152</v>
+        <v>7138212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121585753</v>
+        <v>121585582</v>
       </c>
       <c r="B20" t="n">
-        <v>77993</v>
+        <v>90720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,37 +2768,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691507</v>
+        <v>691728</v>
       </c>
       <c r="R20" t="n">
-        <v>7138234</v>
+        <v>7138256</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2817,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585582</v>
+        <v>121585712</v>
       </c>
       <c r="B21" t="n">
-        <v>90720</v>
+        <v>77993</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,37 +2884,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691728</v>
+        <v>691552</v>
       </c>
       <c r="R21" t="n">
-        <v>7138256</v>
+        <v>7138135</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2933,7 +2943,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2943,7 +2953,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585758</v>
+        <v>121585616</v>
       </c>
       <c r="B22" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,50 +2996,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691640</v>
+        <v>691708</v>
       </c>
       <c r="R22" t="n">
-        <v>7138220</v>
+        <v>7138202</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3058,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3068,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,10 +3100,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585704</v>
+        <v>121585716</v>
       </c>
       <c r="B23" t="n">
-        <v>91988</v>
+        <v>92000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,25 +3112,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3139,10 +3140,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691560</v>
+        <v>691596</v>
       </c>
       <c r="R23" t="n">
-        <v>7138133</v>
+        <v>7138152</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3215,10 +3216,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121585716</v>
+        <v>121585731</v>
       </c>
       <c r="B24" t="n">
-        <v>92000</v>
+        <v>89769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,25 +3228,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3255,7 +3256,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691596</v>
+        <v>691597</v>
       </c>
       <c r="R24" t="n">
         <v>7138152</v>
@@ -3331,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585699</v>
+        <v>121585642</v>
       </c>
       <c r="B25" t="n">
-        <v>92012</v>
+        <v>90667</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3347,37 +3348,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691577</v>
+        <v>691703</v>
       </c>
       <c r="R25" t="n">
-        <v>7138141</v>
+        <v>7138195</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3406,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585752</v>
+        <v>121585657</v>
       </c>
       <c r="B26" t="n">
-        <v>57509</v>
+        <v>90685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,50 +3460,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691505</v>
+        <v>691707</v>
       </c>
       <c r="R26" t="n">
-        <v>7138216</v>
+        <v>7138221</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3531,7 +3523,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3541,7 +3533,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3688,10 +3680,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585694</v>
+        <v>121585723</v>
       </c>
       <c r="B28" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3704,21 +3696,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3728,10 +3720,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691483</v>
+        <v>691505</v>
       </c>
       <c r="R28" t="n">
-        <v>7138215</v>
+        <v>7138208</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3782,7 +3774,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3805,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585633</v>
+        <v>121585729</v>
       </c>
       <c r="B29" t="n">
-        <v>90720</v>
+        <v>77993</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,37 +3812,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691813</v>
+        <v>691479</v>
       </c>
       <c r="R29" t="n">
-        <v>7138277</v>
+        <v>7138224</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3880,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3890,7 +3881,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585642</v>
+        <v>121585758</v>
       </c>
       <c r="B30" t="n">
-        <v>90667</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,37 +3928,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691703</v>
+        <v>691640</v>
       </c>
       <c r="R30" t="n">
-        <v>7138195</v>
+        <v>7138220</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -2520,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585704</v>
+        <v>121585609</v>
       </c>
       <c r="B18" t="n">
-        <v>91988</v>
+        <v>90667</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,37 +2536,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691560</v>
+        <v>691707</v>
       </c>
       <c r="R18" t="n">
-        <v>7138133</v>
+        <v>7138212</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585609</v>
+        <v>121585704</v>
       </c>
       <c r="B19" t="n">
-        <v>90667</v>
+        <v>91988</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,37 +2652,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691707</v>
+        <v>691560</v>
       </c>
       <c r="R19" t="n">
-        <v>7138212</v>
+        <v>7138133</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585712</v>
+        <v>121585716</v>
       </c>
       <c r="B21" t="n">
-        <v>77993</v>
+        <v>92000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,25 +2880,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691552</v>
+        <v>691596</v>
       </c>
       <c r="R21" t="n">
-        <v>7138135</v>
+        <v>7138152</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585716</v>
+        <v>121585712</v>
       </c>
       <c r="B23" t="n">
-        <v>92000</v>
+        <v>77993</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,25 +3112,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691596</v>
+        <v>691552</v>
       </c>
       <c r="R23" t="n">
-        <v>7138152</v>
+        <v>7138135</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585642</v>
+        <v>121585657</v>
       </c>
       <c r="B25" t="n">
-        <v>90667</v>
+        <v>90685</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691703</v>
+        <v>691707</v>
       </c>
       <c r="R25" t="n">
-        <v>7138195</v>
+        <v>7138221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585657</v>
+        <v>121585642</v>
       </c>
       <c r="B26" t="n">
-        <v>90685</v>
+        <v>90667</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691707</v>
+        <v>691703</v>
       </c>
       <c r="R26" t="n">
-        <v>7138221</v>
+        <v>7138195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -2279,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585610</v>
+        <v>121585750</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,37 +2295,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691709</v>
+        <v>691554</v>
       </c>
       <c r="R16" t="n">
-        <v>7138152</v>
+        <v>7138209</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2354,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585750</v>
+        <v>121585610</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,46 +2420,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691554</v>
+        <v>691709</v>
       </c>
       <c r="R17" t="n">
-        <v>7138209</v>
+        <v>7138152</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585716</v>
+        <v>121585712</v>
       </c>
       <c r="B21" t="n">
-        <v>92000</v>
+        <v>77993</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,25 +2880,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691596</v>
+        <v>691552</v>
       </c>
       <c r="R21" t="n">
-        <v>7138152</v>
+        <v>7138135</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585712</v>
+        <v>121585716</v>
       </c>
       <c r="B23" t="n">
-        <v>77993</v>
+        <v>92000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,25 +3112,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691552</v>
+        <v>691596</v>
       </c>
       <c r="R23" t="n">
-        <v>7138135</v>
+        <v>7138152</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585657</v>
+        <v>121585642</v>
       </c>
       <c r="B25" t="n">
-        <v>90685</v>
+        <v>90667</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691707</v>
+        <v>691703</v>
       </c>
       <c r="R25" t="n">
-        <v>7138221</v>
+        <v>7138195</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585642</v>
+        <v>121585657</v>
       </c>
       <c r="B26" t="n">
-        <v>90667</v>
+        <v>90685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691703</v>
+        <v>691707</v>
       </c>
       <c r="R26" t="n">
-        <v>7138195</v>
+        <v>7138221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121585692</v>
+        <v>121585758</v>
       </c>
       <c r="B27" t="n">
-        <v>91996</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3576,38 +3576,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691607</v>
+        <v>691640</v>
       </c>
       <c r="R27" t="n">
-        <v>7138153</v>
+        <v>7138220</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3639,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3680,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585723</v>
+        <v>121585692</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>91996</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,25 +3701,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3720,10 +3729,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691505</v>
+        <v>691607</v>
       </c>
       <c r="R28" t="n">
-        <v>7138208</v>
+        <v>7138153</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3796,10 +3805,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585729</v>
+        <v>121585723</v>
       </c>
       <c r="B29" t="n">
-        <v>77993</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3812,21 +3821,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3836,10 +3845,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691479</v>
+        <v>691505</v>
       </c>
       <c r="R29" t="n">
-        <v>7138224</v>
+        <v>7138208</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3912,10 +3921,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585758</v>
+        <v>121585729</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>77993</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3928,43 +3937,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691640</v>
+        <v>691479</v>
       </c>
       <c r="R30" t="n">
-        <v>7138220</v>
+        <v>7138224</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121282921</v>
       </c>
       <c r="B2" t="n">
-        <v>90685</v>
+        <v>90690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121282919</v>
+        <v>121283094</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>92001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691552</v>
+        <v>691621</v>
       </c>
       <c r="R3" t="n">
-        <v>7138138</v>
+        <v>7138187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283094</v>
+        <v>121282919</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>92001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691621</v>
+        <v>691552</v>
       </c>
       <c r="R4" t="n">
-        <v>7138187</v>
+        <v>7138138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585772</v>
+        <v>121585694</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>78650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691496</v>
+        <v>691483</v>
       </c>
       <c r="R5" t="n">
-        <v>7138158</v>
+        <v>7138215</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585743</v>
+        <v>121585633</v>
       </c>
       <c r="B6" t="n">
-        <v>89419</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,41 +1122,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6286</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691607</v>
+        <v>691813</v>
       </c>
       <c r="R6" t="n">
-        <v>7138152</v>
+        <v>7138277</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585753</v>
+        <v>121585752</v>
       </c>
       <c r="B7" t="n">
-        <v>77993</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1242,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691507</v>
+        <v>691505</v>
       </c>
       <c r="R7" t="n">
-        <v>7138234</v>
+        <v>7138216</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585633</v>
+        <v>121585714</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>92004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,41 +1363,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691813</v>
+        <v>691522</v>
       </c>
       <c r="R8" t="n">
-        <v>7138277</v>
+        <v>7138144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585719</v>
+        <v>121585753</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>78000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1483,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691548</v>
+        <v>691507</v>
       </c>
       <c r="R9" t="n">
-        <v>7138206</v>
+        <v>7138234</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585714</v>
+        <v>121585613</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,41 +1595,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691522</v>
+        <v>691729</v>
       </c>
       <c r="R10" t="n">
-        <v>7138144</v>
+        <v>7138280</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1658,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585695</v>
+        <v>121585642</v>
       </c>
       <c r="B11" t="n">
-        <v>78254</v>
+        <v>90675</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,37 +1715,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691496</v>
+        <v>691703</v>
       </c>
       <c r="R11" t="n">
-        <v>7138229</v>
+        <v>7138195</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1784,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585613</v>
+        <v>121585716</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>92008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,41 +1827,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691729</v>
+        <v>691596</v>
       </c>
       <c r="R12" t="n">
-        <v>7138280</v>
+        <v>7138152</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585699</v>
+        <v>121585657</v>
       </c>
       <c r="B13" t="n">
-        <v>92012</v>
+        <v>90693</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,41 +1943,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691577</v>
+        <v>691707</v>
       </c>
       <c r="R13" t="n">
-        <v>7138141</v>
+        <v>7138221</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585694</v>
+        <v>121585743</v>
       </c>
       <c r="B14" t="n">
-        <v>78643</v>
+        <v>89426</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,25 +2059,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691483</v>
+        <v>691607</v>
       </c>
       <c r="R14" t="n">
-        <v>7138215</v>
+        <v>7138152</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2131,7 +2141,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2154,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585752</v>
+        <v>121585582</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,46 +2179,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691505</v>
+        <v>691728</v>
       </c>
       <c r="R15" t="n">
-        <v>7138216</v>
+        <v>7138256</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585750</v>
+        <v>121585699</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>92020</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,43 +2295,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691554</v>
+        <v>691577</v>
       </c>
       <c r="R16" t="n">
-        <v>7138209</v>
+        <v>7138141</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2363,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2364,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585610</v>
+        <v>121585772</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,37 +2411,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691709</v>
+        <v>691496</v>
       </c>
       <c r="R17" t="n">
-        <v>7138152</v>
+        <v>7138158</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2479,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585609</v>
+        <v>121585719</v>
       </c>
       <c r="B18" t="n">
-        <v>90667</v>
+        <v>90728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,37 +2527,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691707</v>
+        <v>691548</v>
       </c>
       <c r="R18" t="n">
-        <v>7138212</v>
+        <v>7138206</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2595,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585704</v>
+        <v>121585712</v>
       </c>
       <c r="B19" t="n">
-        <v>91988</v>
+        <v>78000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,21 +2643,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2676,10 +2667,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691560</v>
+        <v>691552</v>
       </c>
       <c r="R19" t="n">
-        <v>7138133</v>
+        <v>7138135</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,10 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121585582</v>
+        <v>121585610</v>
       </c>
       <c r="B20" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,21 +2759,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2792,10 +2783,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691728</v>
+        <v>691709</v>
       </c>
       <c r="R20" t="n">
-        <v>7138256</v>
+        <v>7138152</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585712</v>
+        <v>121585729</v>
       </c>
       <c r="B21" t="n">
-        <v>77993</v>
+        <v>78000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,10 +2899,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691552</v>
+        <v>691479</v>
       </c>
       <c r="R21" t="n">
-        <v>7138135</v>
+        <v>7138224</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2984,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585616</v>
+        <v>121585695</v>
       </c>
       <c r="B22" t="n">
-        <v>90685</v>
+        <v>78261</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,41 +2987,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691708</v>
+        <v>691496</v>
       </c>
       <c r="R22" t="n">
-        <v>7138202</v>
+        <v>7138229</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3059,7 +3050,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3060,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3100,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585716</v>
+        <v>121585704</v>
       </c>
       <c r="B23" t="n">
-        <v>92000</v>
+        <v>91996</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,25 +3103,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3140,10 +3131,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691596</v>
+        <v>691560</v>
       </c>
       <c r="R23" t="n">
-        <v>7138152</v>
+        <v>7138133</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3216,10 +3207,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121585731</v>
+        <v>121585758</v>
       </c>
       <c r="B24" t="n">
-        <v>89769</v>
+        <v>57373</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,34 +3223,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691597</v>
+        <v>691640</v>
       </c>
       <c r="R24" t="n">
-        <v>7138152</v>
+        <v>7138220</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585642</v>
+        <v>121585616</v>
       </c>
       <c r="B25" t="n">
-        <v>90667</v>
+        <v>90693</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691703</v>
+        <v>691708</v>
       </c>
       <c r="R25" t="n">
-        <v>7138195</v>
+        <v>7138202</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585657</v>
+        <v>121585609</v>
       </c>
       <c r="B26" t="n">
-        <v>90685</v>
+        <v>90675</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
         <v>691707</v>
       </c>
       <c r="R26" t="n">
-        <v>7138221</v>
+        <v>7138212</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121585758</v>
+        <v>121585731</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>89776</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,43 +3580,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691640</v>
+        <v>691597</v>
       </c>
       <c r="R27" t="n">
-        <v>7138220</v>
+        <v>7138152</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3648,7 +3639,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3649,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3689,10 +3680,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585692</v>
+        <v>121585723</v>
       </c>
       <c r="B28" t="n">
-        <v>91996</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,25 +3692,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3729,10 +3720,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691607</v>
+        <v>691505</v>
       </c>
       <c r="R28" t="n">
-        <v>7138153</v>
+        <v>7138208</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3805,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585723</v>
+        <v>121585692</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>92004</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3817,25 +3808,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3845,10 +3836,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691505</v>
+        <v>691607</v>
       </c>
       <c r="R29" t="n">
-        <v>7138208</v>
+        <v>7138153</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3921,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585729</v>
+        <v>121585750</v>
       </c>
       <c r="B30" t="n">
-        <v>77993</v>
+        <v>57373</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,34 +3928,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691479</v>
+        <v>691554</v>
       </c>
       <c r="R30" t="n">
-        <v>7138224</v>
+        <v>7138209</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585694</v>
+        <v>121585633</v>
       </c>
       <c r="B5" t="n">
-        <v>78650</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,37 +1009,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691483</v>
+        <v>691813</v>
       </c>
       <c r="R5" t="n">
-        <v>7138215</v>
+        <v>7138277</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585633</v>
+        <v>121585694</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>78650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,37 +1125,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691813</v>
+        <v>691483</v>
       </c>
       <c r="R6" t="n">
-        <v>7138277</v>
+        <v>7138215</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,6 +1203,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585729</v>
+        <v>121585695</v>
       </c>
       <c r="B21" t="n">
-        <v>78000</v>
+        <v>78261</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,21 +2875,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691479</v>
+        <v>691496</v>
       </c>
       <c r="R21" t="n">
-        <v>7138224</v>
+        <v>7138229</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585695</v>
+        <v>121585729</v>
       </c>
       <c r="B22" t="n">
-        <v>78261</v>
+        <v>78000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691496</v>
+        <v>691479</v>
       </c>
       <c r="R22" t="n">
-        <v>7138229</v>
+        <v>7138224</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585633</v>
+        <v>121585694</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>78650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,37 +1009,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691813</v>
+        <v>691483</v>
       </c>
       <c r="R5" t="n">
-        <v>7138277</v>
+        <v>7138215</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585694</v>
+        <v>121585633</v>
       </c>
       <c r="B6" t="n">
-        <v>78650</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,37 +1126,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691483</v>
+        <v>691813</v>
       </c>
       <c r="R6" t="n">
-        <v>7138215</v>
+        <v>7138277</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1204,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585699</v>
+        <v>121585694</v>
       </c>
       <c r="B5" t="n">
-        <v>92020</v>
+        <v>78650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691577</v>
+        <v>691483</v>
       </c>
       <c r="R5" t="n">
-        <v>7138141</v>
+        <v>7138215</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585750</v>
+        <v>121585752</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,31 +1126,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691554</v>
+        <v>691505</v>
       </c>
       <c r="R6" t="n">
-        <v>7138209</v>
+        <v>7138216</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1204,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585704</v>
+        <v>121585642</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>90675</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,37 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691560</v>
+        <v>691703</v>
       </c>
       <c r="R7" t="n">
-        <v>7138133</v>
+        <v>7138195</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585752</v>
+        <v>121585729</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>78000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,43 +1367,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691505</v>
+        <v>691479</v>
       </c>
       <c r="R8" t="n">
-        <v>7138216</v>
+        <v>7138224</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1475,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585772</v>
+        <v>121585692</v>
       </c>
       <c r="B9" t="n">
-        <v>79234</v>
+        <v>92004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,25 +1479,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1515,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691496</v>
+        <v>691607</v>
       </c>
       <c r="R9" t="n">
-        <v>7138158</v>
+        <v>7138153</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1591,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585729</v>
+        <v>121585657</v>
       </c>
       <c r="B10" t="n">
-        <v>78000</v>
+        <v>90693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,41 +1595,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691479</v>
+        <v>691707</v>
       </c>
       <c r="R10" t="n">
-        <v>7138224</v>
+        <v>7138221</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585714</v>
+        <v>121585723</v>
       </c>
       <c r="B11" t="n">
-        <v>92004</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,25 +1711,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691522</v>
+        <v>691505</v>
       </c>
       <c r="R11" t="n">
-        <v>7138144</v>
+        <v>7138208</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1939,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585633</v>
+        <v>121585609</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>90675</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1979,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691813</v>
+        <v>691707</v>
       </c>
       <c r="R13" t="n">
-        <v>7138277</v>
+        <v>7138212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585613</v>
+        <v>121585616</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,25 +2059,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691729</v>
+        <v>691708</v>
       </c>
       <c r="R14" t="n">
-        <v>7138280</v>
+        <v>7138202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585731</v>
+        <v>121585699</v>
       </c>
       <c r="B15" t="n">
-        <v>89776</v>
+        <v>92020</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691597</v>
+        <v>691577</v>
       </c>
       <c r="R15" t="n">
-        <v>7138152</v>
+        <v>7138141</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2287,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585723</v>
+        <v>121585753</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>78000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2295,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691505</v>
+        <v>691507</v>
       </c>
       <c r="R16" t="n">
-        <v>7138208</v>
+        <v>7138234</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2403,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585712</v>
+        <v>121585613</v>
       </c>
       <c r="B17" t="n">
-        <v>78000</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,37 +2411,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691552</v>
+        <v>691729</v>
       </c>
       <c r="R17" t="n">
-        <v>7138135</v>
+        <v>7138280</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,7 +2511,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585692</v>
+        <v>121585714</v>
       </c>
       <c r="B18" t="n">
         <v>92004</v>
@@ -2559,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691607</v>
+        <v>691522</v>
       </c>
       <c r="R18" t="n">
-        <v>7138153</v>
+        <v>7138144</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2635,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585616</v>
+        <v>121585582</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,25 +2639,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,10 +2667,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691708</v>
+        <v>691728</v>
       </c>
       <c r="R19" t="n">
-        <v>7138202</v>
+        <v>7138256</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2751,10 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121585743</v>
+        <v>121585731</v>
       </c>
       <c r="B20" t="n">
-        <v>89426</v>
+        <v>89776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,25 +2755,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6286</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2791,7 +2783,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691607</v>
+        <v>691597</v>
       </c>
       <c r="R20" t="n">
         <v>7138152</v>
@@ -2867,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585642</v>
+        <v>121585633</v>
       </c>
       <c r="B21" t="n">
-        <v>90675</v>
+        <v>90728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2883,21 +2875,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2907,10 +2899,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691703</v>
+        <v>691813</v>
       </c>
       <c r="R21" t="n">
-        <v>7138195</v>
+        <v>7138277</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2983,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585582</v>
+        <v>121585772</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>79234</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,37 +2991,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691728</v>
+        <v>691496</v>
       </c>
       <c r="R22" t="n">
-        <v>7138256</v>
+        <v>7138158</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3058,7 +3050,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3068,7 +3060,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585657</v>
+        <v>121585695</v>
       </c>
       <c r="B23" t="n">
-        <v>90693</v>
+        <v>78261</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,41 +3103,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691707</v>
+        <v>691496</v>
       </c>
       <c r="R23" t="n">
-        <v>7138221</v>
+        <v>7138229</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3215,10 +3207,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121585753</v>
+        <v>121585716</v>
       </c>
       <c r="B24" t="n">
-        <v>78000</v>
+        <v>92008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,25 +3219,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3255,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691507</v>
+        <v>691596</v>
       </c>
       <c r="R24" t="n">
-        <v>7138234</v>
+        <v>7138152</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3456,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585609</v>
+        <v>121585704</v>
       </c>
       <c r="B26" t="n">
-        <v>90675</v>
+        <v>91996</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,37 +3464,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691707</v>
+        <v>691560</v>
       </c>
       <c r="R26" t="n">
-        <v>7138212</v>
+        <v>7138133</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3531,7 +3523,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3541,7 +3533,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,10 +3564,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121585694</v>
+        <v>121585750</v>
       </c>
       <c r="B27" t="n">
-        <v>78650</v>
+        <v>57373</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3588,34 +3580,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691483</v>
+        <v>691554</v>
       </c>
       <c r="R27" t="n">
-        <v>7138215</v>
+        <v>7138209</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3647,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3657,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,7 +3667,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585695</v>
+        <v>121585610</v>
       </c>
       <c r="B28" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3705,37 +3705,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691496</v>
+        <v>691709</v>
       </c>
       <c r="R28" t="n">
-        <v>7138229</v>
+        <v>7138152</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3805,10 +3805,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585716</v>
+        <v>121585743</v>
       </c>
       <c r="B29" t="n">
-        <v>92008</v>
+        <v>89426</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691596</v>
+        <v>691607</v>
       </c>
       <c r="R29" t="n">
         <v>7138152</v>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585610</v>
+        <v>121585712</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>78000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,37 +3937,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691709</v>
+        <v>691552</v>
       </c>
       <c r="R30" t="n">
-        <v>7138152</v>
+        <v>7138135</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585642</v>
+        <v>121585729</v>
       </c>
       <c r="B7" t="n">
-        <v>90675</v>
+        <v>78000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,37 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691703</v>
+        <v>691479</v>
       </c>
       <c r="R7" t="n">
-        <v>7138195</v>
+        <v>7138224</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585729</v>
+        <v>121585642</v>
       </c>
       <c r="B8" t="n">
-        <v>78000</v>
+        <v>90675</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,37 +1367,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691479</v>
+        <v>691703</v>
       </c>
       <c r="R8" t="n">
-        <v>7138224</v>
+        <v>7138195</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585719</v>
+        <v>121585609</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>90675</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,37 +1831,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691548</v>
+        <v>691707</v>
       </c>
       <c r="R12" t="n">
-        <v>7138206</v>
+        <v>7138212</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585609</v>
+        <v>121585616</v>
       </c>
       <c r="B13" t="n">
-        <v>90675</v>
+        <v>90693</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,25 +1943,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691707</v>
+        <v>691708</v>
       </c>
       <c r="R13" t="n">
-        <v>7138212</v>
+        <v>7138202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585616</v>
+        <v>121585719</v>
       </c>
       <c r="B14" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,41 +2059,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691708</v>
+        <v>691548</v>
       </c>
       <c r="R14" t="n">
-        <v>7138202</v>
+        <v>7138206</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38164-2023 artfynd.xlsx
+++ b/artfynd/A 38164-2023 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585694</v>
+        <v>121585758</v>
       </c>
       <c r="B5" t="n">
-        <v>78650</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691483</v>
+        <v>691640</v>
       </c>
       <c r="R5" t="n">
-        <v>7138215</v>
+        <v>7138220</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1096,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585752</v>
+        <v>121585695</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>78261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,43 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691505</v>
+        <v>691496</v>
       </c>
       <c r="R6" t="n">
-        <v>7138216</v>
+        <v>7138229</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585729</v>
+        <v>121585712</v>
       </c>
       <c r="B7" t="n">
         <v>78000</v>
@@ -1275,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691479</v>
+        <v>691552</v>
       </c>
       <c r="R7" t="n">
-        <v>7138224</v>
+        <v>7138135</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1351,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585642</v>
+        <v>121585731</v>
       </c>
       <c r="B8" t="n">
-        <v>90675</v>
+        <v>89776</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,37 +1366,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691703</v>
+        <v>691597</v>
       </c>
       <c r="R8" t="n">
-        <v>7138195</v>
+        <v>7138152</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585692</v>
+        <v>121585582</v>
       </c>
       <c r="B9" t="n">
-        <v>92004</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,41 +1478,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691607</v>
+        <v>691728</v>
       </c>
       <c r="R9" t="n">
-        <v>7138153</v>
+        <v>7138256</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585657</v>
+        <v>121585719</v>
       </c>
       <c r="B10" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,41 +1594,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691707</v>
+        <v>691548</v>
       </c>
       <c r="R10" t="n">
-        <v>7138221</v>
+        <v>7138206</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585723</v>
+        <v>121585716</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>92008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691505</v>
+        <v>691596</v>
       </c>
       <c r="R11" t="n">
-        <v>7138208</v>
+        <v>7138152</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1815,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585609</v>
+        <v>121585753</v>
       </c>
       <c r="B12" t="n">
-        <v>90675</v>
+        <v>78000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,37 +1830,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691707</v>
+        <v>691507</v>
       </c>
       <c r="R12" t="n">
-        <v>7138212</v>
+        <v>7138234</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585616</v>
+        <v>121585699</v>
       </c>
       <c r="B13" t="n">
-        <v>90693</v>
+        <v>92020</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,41 +1942,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691708</v>
+        <v>691577</v>
       </c>
       <c r="R13" t="n">
-        <v>7138202</v>
+        <v>7138141</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585719</v>
+        <v>121585743</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>89426</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,25 +2058,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2087,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691548</v>
+        <v>691607</v>
       </c>
       <c r="R14" t="n">
-        <v>7138206</v>
+        <v>7138152</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2163,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585699</v>
+        <v>121585714</v>
       </c>
       <c r="B15" t="n">
-        <v>92020</v>
+        <v>92004</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,25 +2174,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691577</v>
+        <v>691522</v>
       </c>
       <c r="R15" t="n">
-        <v>7138141</v>
+        <v>7138144</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2279,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585753</v>
+        <v>121585657</v>
       </c>
       <c r="B16" t="n">
-        <v>78000</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,41 +2290,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691507</v>
+        <v>691707</v>
       </c>
       <c r="R16" t="n">
-        <v>7138234</v>
+        <v>7138221</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2354,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121585613</v>
+        <v>121585772</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>79234</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,37 +2410,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691729</v>
+        <v>691496</v>
       </c>
       <c r="R17" t="n">
-        <v>7138280</v>
+        <v>7138158</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2470,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121585714</v>
+        <v>121585642</v>
       </c>
       <c r="B18" t="n">
-        <v>92004</v>
+        <v>90675</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,41 +2522,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691522</v>
+        <v>691703</v>
       </c>
       <c r="R18" t="n">
-        <v>7138144</v>
+        <v>7138195</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2586,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121585582</v>
+        <v>121585692</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>92004</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,41 +2638,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691728</v>
+        <v>691607</v>
       </c>
       <c r="R19" t="n">
-        <v>7138256</v>
+        <v>7138153</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2702,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121585731</v>
+        <v>121585750</v>
       </c>
       <c r="B20" t="n">
-        <v>89776</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,34 +2758,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691597</v>
+        <v>691554</v>
       </c>
       <c r="R20" t="n">
-        <v>7138152</v>
+        <v>7138209</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2818,7 +2826,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2836,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121585633</v>
+        <v>121585752</v>
       </c>
       <c r="B21" t="n">
-        <v>90728</v>
+        <v>57510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,37 +2883,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691813</v>
+        <v>691505</v>
       </c>
       <c r="R21" t="n">
-        <v>7138277</v>
+        <v>7138216</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2934,7 +2951,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2961,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121585772</v>
+        <v>121585694</v>
       </c>
       <c r="B22" t="n">
-        <v>79234</v>
+        <v>78650</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +3008,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3015,10 +3032,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691496</v>
+        <v>691483</v>
       </c>
       <c r="R22" t="n">
-        <v>7138158</v>
+        <v>7138215</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3069,6 +3086,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3091,10 +3109,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121585695</v>
+        <v>121585609</v>
       </c>
       <c r="B23" t="n">
-        <v>78261</v>
+        <v>90675</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3107,37 +3125,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691496</v>
+        <v>691707</v>
       </c>
       <c r="R23" t="n">
-        <v>7138229</v>
+        <v>7138212</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3166,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3207,10 +3225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121585716</v>
+        <v>121585704</v>
       </c>
       <c r="B24" t="n">
-        <v>92008</v>
+        <v>91996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3219,25 +3237,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3247,10 +3265,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691596</v>
+        <v>691560</v>
       </c>
       <c r="R24" t="n">
-        <v>7138152</v>
+        <v>7138133</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3323,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121585758</v>
+        <v>121585613</v>
       </c>
       <c r="B25" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,46 +3357,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691640</v>
+        <v>691729</v>
       </c>
       <c r="R25" t="n">
-        <v>7138220</v>
+        <v>7138280</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3407,7 +3416,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3426,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121585704</v>
+        <v>121585729</v>
       </c>
       <c r="B26" t="n">
-        <v>91996</v>
+        <v>78000</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,21 +3473,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691560</v>
+        <v>691479</v>
       </c>
       <c r="R26" t="n">
-        <v>7138133</v>
+        <v>7138224</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3564,10 +3573,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121585750</v>
+        <v>121585633</v>
       </c>
       <c r="B27" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,46 +3589,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691554</v>
+        <v>691813</v>
       </c>
       <c r="R27" t="n">
-        <v>7138209</v>
+        <v>7138277</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3689,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121585610</v>
+        <v>121585616</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,25 +3701,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691709</v>
+        <v>691708</v>
       </c>
       <c r="R28" t="n">
-        <v>7138152</v>
+        <v>7138202</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3805,10 +3805,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121585743</v>
+        <v>121585610</v>
       </c>
       <c r="B29" t="n">
-        <v>89426</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3817,41 +3817,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6286</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691607</v>
+        <v>691709</v>
       </c>
       <c r="R29" t="n">
         <v>7138152</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,10 +3921,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121585712</v>
+        <v>121585723</v>
       </c>
       <c r="B30" t="n">
-        <v>78000</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,21 +3937,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691552</v>
+        <v>691505</v>
       </c>
       <c r="R30" t="n">
-        <v>7138135</v>
+        <v>7138208</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
